--- a/Excel_jumia_dataset.xlsx
+++ b/Excel_jumia_dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javan\Desktop\Jumia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javan\Desktop\Jumia\Jumia_Product_Performance_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC1E9FB-DCC5-4F4B-B97D-DBCDBF7B9290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F556B953-CAE8-443C-8BF4-876A73D46180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{720439CB-7872-429C-94DD-03C07880A471}"/>
+    <workbookView xWindow="3600" yWindow="3600" windowWidth="14400" windowHeight="7340" firstSheet="1" activeTab="4" xr2:uid="{720439CB-7872-429C-94DD-03C07880A471}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel_jumia_dataset" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2158,24 +2158,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2185,8 +2167,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -18128,7 +18128,1040 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F36809F0-5F72-4343-8C12-581BE2C3BF82}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{896C9B17-5049-4235-98A2-4339E6CD5682}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="H18:I29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="110">
+        <item x="38"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="27"/>
+        <item x="31"/>
+        <item x="61"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="101"/>
+        <item x="80"/>
+        <item x="5"/>
+        <item x="100"/>
+        <item x="91"/>
+        <item x="47"/>
+        <item x="73"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="19"/>
+        <item x="74"/>
+        <item x="20"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="58"/>
+        <item x="28"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="79"/>
+        <item x="60"/>
+        <item x="106"/>
+        <item x="90"/>
+        <item x="45"/>
+        <item x="76"/>
+        <item x="71"/>
+        <item x="97"/>
+        <item x="99"/>
+        <item x="67"/>
+        <item x="56"/>
+        <item x="15"/>
+        <item x="64"/>
+        <item x="96"/>
+        <item x="42"/>
+        <item x="78"/>
+        <item x="108"/>
+        <item x="49"/>
+        <item x="46"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="44"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="75"/>
+        <item x="53"/>
+        <item x="7"/>
+        <item x="35"/>
+        <item x="72"/>
+        <item x="25"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="98"/>
+        <item x="68"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="39"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="102"/>
+        <item x="18"/>
+        <item x="77"/>
+        <item x="1"/>
+        <item x="95"/>
+        <item x="41"/>
+        <item x="14"/>
+        <item x="86"/>
+        <item x="29"/>
+        <item x="52"/>
+        <item x="59"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="16"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="93"/>
+        <item x="26"/>
+        <item x="88"/>
+        <item x="37"/>
+        <item x="89"/>
+        <item x="43"/>
+        <item x="104"/>
+        <item x="54"/>
+        <item x="105"/>
+        <item x="63"/>
+        <item x="87"/>
+        <item x="92"/>
+        <item x="107"/>
+        <item x="85"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="70"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Review" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B06BF4F-6313-49C4-BD21-FA374C57CBA6}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="M2:N13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="110">
+        <item x="38"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="27"/>
+        <item x="31"/>
+        <item x="61"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="101"/>
+        <item x="80"/>
+        <item x="5"/>
+        <item x="100"/>
+        <item x="91"/>
+        <item x="47"/>
+        <item x="73"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="19"/>
+        <item x="74"/>
+        <item x="20"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="58"/>
+        <item x="28"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="79"/>
+        <item x="60"/>
+        <item x="106"/>
+        <item x="90"/>
+        <item x="45"/>
+        <item x="76"/>
+        <item x="71"/>
+        <item x="97"/>
+        <item x="99"/>
+        <item x="67"/>
+        <item x="56"/>
+        <item x="15"/>
+        <item x="64"/>
+        <item x="96"/>
+        <item x="42"/>
+        <item x="78"/>
+        <item x="108"/>
+        <item x="49"/>
+        <item x="46"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="44"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="75"/>
+        <item x="53"/>
+        <item x="7"/>
+        <item x="35"/>
+        <item x="72"/>
+        <item x="25"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="98"/>
+        <item x="68"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="39"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="102"/>
+        <item x="18"/>
+        <item x="77"/>
+        <item x="1"/>
+        <item x="95"/>
+        <item x="41"/>
+        <item x="14"/>
+        <item x="86"/>
+        <item x="29"/>
+        <item x="52"/>
+        <item x="59"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="16"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="93"/>
+        <item x="26"/>
+        <item x="88"/>
+        <item x="37"/>
+        <item x="89"/>
+        <item x="43"/>
+        <item x="104"/>
+        <item x="54"/>
+        <item x="105"/>
+        <item x="63"/>
+        <item x="87"/>
+        <item x="92"/>
+        <item x="107"/>
+        <item x="85"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="70"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Discount" fld="3" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E90E1293-A1A4-498C-B250-4945E99DEACE}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="H2:I13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="110">
+        <item x="38"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="27"/>
+        <item x="31"/>
+        <item x="61"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="101"/>
+        <item x="80"/>
+        <item x="5"/>
+        <item x="100"/>
+        <item x="91"/>
+        <item x="47"/>
+        <item x="73"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="19"/>
+        <item x="74"/>
+        <item x="20"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="58"/>
+        <item x="28"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="79"/>
+        <item x="60"/>
+        <item x="106"/>
+        <item x="90"/>
+        <item x="45"/>
+        <item x="76"/>
+        <item x="71"/>
+        <item x="97"/>
+        <item x="99"/>
+        <item x="67"/>
+        <item x="56"/>
+        <item x="15"/>
+        <item x="64"/>
+        <item x="96"/>
+        <item x="42"/>
+        <item x="78"/>
+        <item x="108"/>
+        <item x="49"/>
+        <item x="46"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="44"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="75"/>
+        <item x="53"/>
+        <item x="7"/>
+        <item x="35"/>
+        <item x="72"/>
+        <item x="25"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="98"/>
+        <item x="68"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="39"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="102"/>
+        <item x="18"/>
+        <item x="77"/>
+        <item x="1"/>
+        <item x="95"/>
+        <item x="41"/>
+        <item x="14"/>
+        <item x="86"/>
+        <item x="29"/>
+        <item x="52"/>
+        <item x="59"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="16"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="93"/>
+        <item x="26"/>
+        <item x="88"/>
+        <item x="37"/>
+        <item x="89"/>
+        <item x="43"/>
+        <item x="104"/>
+        <item x="54"/>
+        <item x="105"/>
+        <item x="63"/>
+        <item x="87"/>
+        <item x="92"/>
+        <item x="107"/>
+        <item x="85"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="70"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Rating" fld="5" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{75D11773-3987-4FAC-B9CD-FFDC0180378C}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A24:B28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Review" fld="4" subtotal="average" baseField="7" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49DCB90C-25D0-4471-842C-EAB3A6161C2D}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A14:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="24">
+        <item x="22"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Product" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2AF5F631-7036-48A8-847A-F5E069235E07}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Product" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F36809F0-5F72-4343-8C12-581BE2C3BF82}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="M18:R23" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -18375,1039 +19408,6 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{896C9B17-5049-4235-98A2-4339E6CD5682}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="H18:I29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="110">
-        <item x="38"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="27"/>
-        <item x="31"/>
-        <item x="61"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="101"/>
-        <item x="80"/>
-        <item x="5"/>
-        <item x="100"/>
-        <item x="91"/>
-        <item x="47"/>
-        <item x="73"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="19"/>
-        <item x="74"/>
-        <item x="20"/>
-        <item x="94"/>
-        <item x="12"/>
-        <item x="40"/>
-        <item x="21"/>
-        <item x="58"/>
-        <item x="28"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="79"/>
-        <item x="60"/>
-        <item x="106"/>
-        <item x="90"/>
-        <item x="45"/>
-        <item x="76"/>
-        <item x="71"/>
-        <item x="97"/>
-        <item x="99"/>
-        <item x="67"/>
-        <item x="56"/>
-        <item x="15"/>
-        <item x="64"/>
-        <item x="96"/>
-        <item x="42"/>
-        <item x="78"/>
-        <item x="108"/>
-        <item x="49"/>
-        <item x="46"/>
-        <item x="83"/>
-        <item x="103"/>
-        <item x="44"/>
-        <item x="55"/>
-        <item x="36"/>
-        <item x="48"/>
-        <item x="75"/>
-        <item x="53"/>
-        <item x="7"/>
-        <item x="35"/>
-        <item x="72"/>
-        <item x="25"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="98"/>
-        <item x="68"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="39"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="102"/>
-        <item x="18"/>
-        <item x="77"/>
-        <item x="1"/>
-        <item x="95"/>
-        <item x="41"/>
-        <item x="14"/>
-        <item x="86"/>
-        <item x="29"/>
-        <item x="52"/>
-        <item x="59"/>
-        <item x="82"/>
-        <item x="84"/>
-        <item x="16"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="93"/>
-        <item x="26"/>
-        <item x="88"/>
-        <item x="37"/>
-        <item x="89"/>
-        <item x="43"/>
-        <item x="104"/>
-        <item x="54"/>
-        <item x="105"/>
-        <item x="63"/>
-        <item x="87"/>
-        <item x="92"/>
-        <item x="107"/>
-        <item x="85"/>
-        <item x="69"/>
-        <item x="3"/>
-        <item x="70"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="59"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="95"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="91"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Review" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E90E1293-A1A4-498C-B250-4945E99DEACE}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="H2:I13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="110">
-        <item x="38"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="27"/>
-        <item x="31"/>
-        <item x="61"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="101"/>
-        <item x="80"/>
-        <item x="5"/>
-        <item x="100"/>
-        <item x="91"/>
-        <item x="47"/>
-        <item x="73"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="19"/>
-        <item x="74"/>
-        <item x="20"/>
-        <item x="94"/>
-        <item x="12"/>
-        <item x="40"/>
-        <item x="21"/>
-        <item x="58"/>
-        <item x="28"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="79"/>
-        <item x="60"/>
-        <item x="106"/>
-        <item x="90"/>
-        <item x="45"/>
-        <item x="76"/>
-        <item x="71"/>
-        <item x="97"/>
-        <item x="99"/>
-        <item x="67"/>
-        <item x="56"/>
-        <item x="15"/>
-        <item x="64"/>
-        <item x="96"/>
-        <item x="42"/>
-        <item x="78"/>
-        <item x="108"/>
-        <item x="49"/>
-        <item x="46"/>
-        <item x="83"/>
-        <item x="103"/>
-        <item x="44"/>
-        <item x="55"/>
-        <item x="36"/>
-        <item x="48"/>
-        <item x="75"/>
-        <item x="53"/>
-        <item x="7"/>
-        <item x="35"/>
-        <item x="72"/>
-        <item x="25"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="98"/>
-        <item x="68"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="39"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="102"/>
-        <item x="18"/>
-        <item x="77"/>
-        <item x="1"/>
-        <item x="95"/>
-        <item x="41"/>
-        <item x="14"/>
-        <item x="86"/>
-        <item x="29"/>
-        <item x="52"/>
-        <item x="59"/>
-        <item x="82"/>
-        <item x="84"/>
-        <item x="16"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="93"/>
-        <item x="26"/>
-        <item x="88"/>
-        <item x="37"/>
-        <item x="89"/>
-        <item x="43"/>
-        <item x="104"/>
-        <item x="54"/>
-        <item x="105"/>
-        <item x="63"/>
-        <item x="87"/>
-        <item x="92"/>
-        <item x="107"/>
-        <item x="85"/>
-        <item x="69"/>
-        <item x="3"/>
-        <item x="70"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="65"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="90"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Rating" fld="5" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{75D11773-3987-4FAC-B9CD-FFDC0180378C}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A24:B28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Review" fld="4" subtotal="average" baseField="7" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49DCB90C-25D0-4471-842C-EAB3A6161C2D}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A14:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="24">
-        <item x="22"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Product" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2AF5F631-7036-48A8-847A-F5E069235E07}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Product" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B06BF4F-6313-49C4-BD21-FA374C57CBA6}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="M2:N13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="110">
-        <item x="38"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="27"/>
-        <item x="31"/>
-        <item x="61"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="101"/>
-        <item x="80"/>
-        <item x="5"/>
-        <item x="100"/>
-        <item x="91"/>
-        <item x="47"/>
-        <item x="73"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="19"/>
-        <item x="74"/>
-        <item x="20"/>
-        <item x="94"/>
-        <item x="12"/>
-        <item x="40"/>
-        <item x="21"/>
-        <item x="58"/>
-        <item x="28"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="79"/>
-        <item x="60"/>
-        <item x="106"/>
-        <item x="90"/>
-        <item x="45"/>
-        <item x="76"/>
-        <item x="71"/>
-        <item x="97"/>
-        <item x="99"/>
-        <item x="67"/>
-        <item x="56"/>
-        <item x="15"/>
-        <item x="64"/>
-        <item x="96"/>
-        <item x="42"/>
-        <item x="78"/>
-        <item x="108"/>
-        <item x="49"/>
-        <item x="46"/>
-        <item x="83"/>
-        <item x="103"/>
-        <item x="44"/>
-        <item x="55"/>
-        <item x="36"/>
-        <item x="48"/>
-        <item x="75"/>
-        <item x="53"/>
-        <item x="7"/>
-        <item x="35"/>
-        <item x="72"/>
-        <item x="25"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="98"/>
-        <item x="68"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="39"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="102"/>
-        <item x="18"/>
-        <item x="77"/>
-        <item x="1"/>
-        <item x="95"/>
-        <item x="41"/>
-        <item x="14"/>
-        <item x="86"/>
-        <item x="29"/>
-        <item x="52"/>
-        <item x="59"/>
-        <item x="82"/>
-        <item x="84"/>
-        <item x="16"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="93"/>
-        <item x="26"/>
-        <item x="88"/>
-        <item x="37"/>
-        <item x="89"/>
-        <item x="43"/>
-        <item x="104"/>
-        <item x="54"/>
-        <item x="105"/>
-        <item x="63"/>
-        <item x="87"/>
-        <item x="92"/>
-        <item x="107"/>
-        <item x="85"/>
-        <item x="69"/>
-        <item x="3"/>
-        <item x="70"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField dataField="1" numFmtId="10" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="67"/>
-    </i>
-    <i>
-      <x v="84"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Discount" fld="3" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -26875,9 +26875,9 @@
       <c r="I1" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -26887,19 +26887,19 @@
         <f>ROWS(tblProducts[Product])</f>
         <v>115</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="19" t="s">
         <v>486</v>
       </c>
       <c r="N2" s="10"/>
@@ -26912,11 +26912,11 @@
         <f>AVERAGE(tblProducts[Current price (Ksh)])</f>
         <v>1172.7913043478261</v>
       </c>
-      <c r="I3" s="21" t="str" cm="1">
+      <c r="I3" s="15" t="str" cm="1">
         <f t="array" ref="I3:I24">_xlfn._xlws.FILTER(tblProducts[Product],(tblProducts[Discount category]="High Discount")*(tblProducts[Rating category]&lt;&gt;"Excellent")*(tblProducts[Rating category]&lt;&gt;"Missing"))</f>
         <v>Metal Decorative Hooks Key Hangers Entryway Wall Hooks Towel Hooks - Home</v>
       </c>
-      <c r="J3" s="21" cm="1">
+      <c r="J3" s="15" cm="1">
         <f t="array" ref="J3:J24">_xlfn._xlws.FILTER(tblProducts[Discount],(tblProducts[Discount category]="High Discount")*(tblProducts[Rating category]&lt;&gt;"Excellent")*(tblProducts[Rating category]&lt;&gt;"Missing"))</f>
         <v>0.47</v>
       </c>
@@ -26924,7 +26924,7 @@
         <f t="array" ref="K3:K24">_xlfn._xlws.FILTER(tblProducts[Discount category],(tblProducts[Discount category]="High Discount")*(tblProducts[Rating category]&lt;&gt;"Excellent")*(tblProducts[Rating category]&lt;&gt;"Missing"))</f>
         <v>High Discount</v>
       </c>
-      <c r="L3" s="21" cm="1">
+      <c r="L3" s="15" cm="1">
         <f t="array" ref="L3:L24">_xlfn._xlws.FILTER(tblProducts[Rating],(tblProducts[Discount category]="High Discount")*(tblProducts[Rating category]&lt;&gt;"Excellent")*(tblProducts[Rating category]&lt;&gt;"Missing"))</f>
         <v>4.0999999999999996</v>
       </c>
@@ -26941,16 +26941,16 @@
         <f>AVERAGE(tblProducts[Discount])</f>
         <v>0.36956521739130432</v>
       </c>
-      <c r="I4" s="21" t="str">
+      <c r="I4" s="15" t="str">
         <v>13 In 1 Home Repair Tools Box Kit Set</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="15">
         <v>0.45</v>
       </c>
       <c r="K4" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="15">
         <v>3.8</v>
       </c>
       <c r="M4" t="str">
@@ -26965,16 +26965,16 @@
         <f>AVERAGE(tblProducts[Rating])</f>
         <v>3.8894736842105258</v>
       </c>
-      <c r="I5" s="21" t="str">
+      <c r="I5" s="15" t="str">
         <v>Lasa Digital Thermometer And Hydrometer</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="15">
         <v>0.42</v>
       </c>
       <c r="K5" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="15">
         <v>4.5</v>
       </c>
       <c r="M5" t="str">
@@ -26989,16 +26989,16 @@
         <f>SUM(tblProducts[Review])</f>
         <v>723</v>
       </c>
-      <c r="I6" s="21" t="str">
+      <c r="I6" s="15" t="str">
         <v>3Pcs Single Head Knitting Crochet Sweater Needle Set</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="15">
         <v>0.53</v>
       </c>
       <c r="K6" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="15">
         <v>3.3</v>
       </c>
       <c r="M6" t="str">
@@ -27013,16 +27013,16 @@
         <f>COUNTIFS(tblProducts[Discount category],"High Discount",tblProducts[Rating category],"&lt;&gt;Excellent",tblProducts[Rating category],"&lt;&gt;Missing")</f>
         <v>22</v>
       </c>
-      <c r="I7" s="21" t="str">
+      <c r="I7" s="15" t="str">
         <v>Lasa 3 Tier Bamboo Shoe Bench Storage Shelf</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="15">
         <v>0.54</v>
       </c>
       <c r="K7" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="15">
         <v>4.3</v>
       </c>
       <c r="M7" t="str">
@@ -27030,46 +27030,46 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="I8" s="21" t="str">
+      <c r="I8" s="15" t="str">
         <v>Exfoliate And Exfoliate Face Towel - Black</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="15">
         <v>0.52</v>
       </c>
       <c r="K8" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="15">
         <v>4.3</v>
       </c>
       <c r="M8" t="str">
         <v>Average</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>381</v>
       </c>
       <c r="B9" t="s">
         <v>389</v>
       </c>
-      <c r="I9" s="21" t="str">
+      <c r="I9" s="15" t="str">
         <v>LED Eye Protection Desk Lamp , Study, Reading, USB Fan - Double Pen Holder</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="15">
         <v>0.48</v>
       </c>
       <c r="K9" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="15">
         <v>4.3</v>
       </c>
       <c r="M9" t="str">
         <v>Average</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>384</v>
       </c>
@@ -27077,23 +27077,23 @@
         <f>CORREL(tblProducts[Discount],tblProducts[Review])</f>
         <v>-0.13682272428088296</v>
       </c>
-      <c r="I10" s="21" t="str">
+      <c r="I10" s="15" t="str">
         <v>Punch-Free Great Load Bearing Bathroom Storage Rack Wall Shelf-White</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="15">
         <v>0.41</v>
       </c>
       <c r="K10" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="15">
         <v>4.3</v>
       </c>
       <c r="M10" t="str">
         <v>Average</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>382</v>
       </c>
@@ -27101,23 +27101,23 @@
         <f>CORREL(tblProducts[Rating],tblProducts[Review])</f>
         <v>5.7209035119876482E-2</v>
       </c>
-      <c r="I11" s="21" t="str">
+      <c r="I11" s="15" t="str">
         <v>Mythco 120Cob Solar Wall Ligt With Motion Sensor And Remote Control 3 Modes</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="15">
         <v>0.54</v>
       </c>
       <c r="K11" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="15">
         <v>3</v>
       </c>
       <c r="M11" t="str">
         <v>Average</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>383</v>
       </c>
@@ -27125,33 +27125,33 @@
         <f>CORREL(tblProducts[Current price (Ksh)],tblProducts[Rating])</f>
         <v>0.10797680009158267</v>
       </c>
-      <c r="I12" s="21" t="str">
+      <c r="I12" s="15" t="str">
         <v>5-Pcs Stainless Steel Cooking Pot Set With Steamed Slices</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="15">
         <v>0.55000000000000004</v>
       </c>
       <c r="K12" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="15">
         <v>2.1</v>
       </c>
       <c r="M12" t="str">
         <v>Poor</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="I13" s="21" t="str">
+    <row r="13" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="I13" s="15" t="str">
         <v>120W Cordless Vacuum Cleaners Handheld Electric Vacuum Cleaner</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="15">
         <v>0.49</v>
       </c>
       <c r="K13" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="15">
         <v>2.8</v>
       </c>
       <c r="M13" t="str">
@@ -27162,16 +27162,16 @@
       <c r="A14" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="I14" s="21" t="str">
+      <c r="I14" s="15" t="str">
         <v>Intelligent LED Body Sensor Wireless Lighting Night Light USB</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="15">
         <v>0.52</v>
       </c>
       <c r="K14" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="15">
         <v>2.7</v>
       </c>
       <c r="M14" t="str">
@@ -27191,16 +27191,16 @@
       <c r="D15" t="s">
         <v>388</v>
       </c>
-      <c r="I15" s="21" t="str">
+      <c r="I15" s="15" t="str">
         <v>Artificial Potted Flowers Room Decorative Flowers (2 Pieces)</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="15">
         <v>0.45</v>
       </c>
       <c r="K15" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="15">
         <v>2.2000000000000002</v>
       </c>
       <c r="M15" t="str">
@@ -27223,16 +27223,16 @@
         <f>INDEX(tblProducts[Rating],MATCH(C16,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I16" s="21" t="str">
+      <c r="I16" s="15" t="str">
         <v>380Ml USB Rechargeable Portable Small Blenders And Juicers</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="15">
         <v>0.5</v>
       </c>
       <c r="K16" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="15">
         <v>2.2999999999999998</v>
       </c>
       <c r="M16" t="str">
@@ -27255,23 +27255,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C17,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I17" s="21" t="str">
+      <c r="I17" s="15" t="str">
         <v>Agapeon Toothbrush Holder And Toothpaste Dispenser</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="15">
         <v>0.45</v>
       </c>
       <c r="K17" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="15">
         <v>2.6</v>
       </c>
       <c r="M17" t="str">
         <v>Poor</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>3</v>
       </c>
@@ -27287,23 +27287,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C18,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I18" s="21" t="str">
+      <c r="I18" s="15" t="str">
         <v>Watercolour Gold Foil Textured Print Pillow Cover</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="15">
         <v>0.43</v>
       </c>
       <c r="K18" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L18" s="21">
+      <c r="L18" s="15">
         <v>2.2999999999999998</v>
       </c>
       <c r="M18" t="str">
         <v>Poor</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>4</v>
       </c>
@@ -27319,16 +27319,16 @@
         <f>INDEX(tblProducts[Rating],MATCH(C19,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I19" s="21" t="str">
+      <c r="I19" s="15" t="str">
         <v>Wrought Iron Bathroom Shelf Wall Mounted Free Punch Toilet Rack</v>
       </c>
-      <c r="J19" s="21">
+      <c r="J19" s="15">
         <v>0.43</v>
       </c>
       <c r="K19" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L19" s="21">
+      <c r="L19" s="15">
         <v>3</v>
       </c>
       <c r="M19" t="str">
@@ -27351,23 +27351,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C20,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I20" s="21" t="str">
+      <c r="I20" s="15" t="str">
         <v>7-Piece Set Of Storage Bags, Travel Storage Bags, Shoe Bags</v>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="15">
         <v>0.47</v>
       </c>
       <c r="K20" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L20" s="21">
+      <c r="L20" s="15">
         <v>2.2000000000000002</v>
       </c>
       <c r="M20" t="str">
         <v>Poor</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>6</v>
       </c>
@@ -27383,23 +27383,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C21,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I21" s="21" t="str">
+      <c r="I21" s="15" t="str">
         <v>Electric LED UV Mosquito Killer Lamp, Outdoor/Indoor Fly Killer Trap Light -USB</v>
       </c>
-      <c r="J21" s="21">
+      <c r="J21" s="15">
         <v>0.47</v>
       </c>
       <c r="K21" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L21" s="21">
+      <c r="L21" s="15">
         <v>2.1</v>
       </c>
       <c r="M21" t="str">
         <v>Poor</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>7</v>
       </c>
@@ -27415,23 +27415,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C22,tblProducts[Rating Rank Key],0))</f>
         <v>5</v>
       </c>
-      <c r="I22" s="21" t="str">
+      <c r="I22" s="15" t="str">
         <v>Memory Foam Neck Pillow Cover, With Pillow Core - 50*30Cm</v>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="15">
         <v>0.46</v>
       </c>
       <c r="K22" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L22" s="21">
+      <c r="L22" s="15">
         <v>3</v>
       </c>
       <c r="M22" t="str">
         <v>Average</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>8</v>
       </c>
@@ -27447,23 +27447,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C23,tblProducts[Rating Rank Key],0))</f>
         <v>4.8</v>
       </c>
-      <c r="I23" s="21" t="str">
+      <c r="I23" s="15" t="str">
         <v>Household Pineapple Peeler Peeler</v>
       </c>
-      <c r="J23" s="21">
+      <c r="J23" s="15">
         <v>0.49</v>
       </c>
       <c r="K23" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L23" s="21">
+      <c r="L23" s="15">
         <v>4</v>
       </c>
       <c r="M23" t="str">
         <v>Average</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>9</v>
       </c>
@@ -27479,23 +27479,23 @@
         <f>INDEX(tblProducts[Rating],MATCH(C24,tblProducts[Rating Rank Key],0))</f>
         <v>4.8</v>
       </c>
-      <c r="I24" s="21" t="str">
+      <c r="I24" s="15" t="str">
         <v>Wall-Mounted Sticker Punch-Free Plug Fixer</v>
       </c>
-      <c r="J24" s="21">
+      <c r="J24" s="15">
         <v>0.5</v>
       </c>
       <c r="K24" t="str">
         <v>High Discount</v>
       </c>
-      <c r="L24" s="21">
+      <c r="L24" s="15">
         <v>2</v>
       </c>
       <c r="M24" t="str">
         <v>Poor</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>10</v>
       </c>
@@ -27511,9 +27511,9 @@
         <f>INDEX(tblProducts[Rating],MATCH(C25,tblProducts[Rating Rank Key],0))</f>
         <v>4.8</v>
       </c>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="L25" s="21"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="L25" s="15"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
@@ -28456,112 +28456,112 @@
       <c r="M5" s="14"/>
     </row>
     <row r="7" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16">
+      <c r="C7" s="26"/>
+      <c r="D7" s="25">
         <f>Analysis!B2</f>
         <v>115</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="G7" s="15" t="s">
+      <c r="E7" s="25"/>
+      <c r="G7" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="16">
+      <c r="H7" s="26"/>
+      <c r="I7" s="25">
         <f>Analysis!B3</f>
         <v>1172.7913043478261</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="L7" s="15" t="s">
+      <c r="J7" s="25"/>
+      <c r="L7" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="M7" s="15"/>
-      <c r="N7" s="16">
+      <c r="M7" s="26"/>
+      <c r="N7" s="25">
         <f>Analysis!B4</f>
         <v>0.36956521739130432</v>
       </c>
-      <c r="O7" s="16"/>
-      <c r="Q7" s="15" t="s">
+      <c r="O7" s="25"/>
+      <c r="Q7" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="R7" s="15"/>
-      <c r="S7" s="16">
+      <c r="R7" s="26"/>
+      <c r="S7" s="25">
         <f>Analysis!B5</f>
         <v>3.8894736842105258</v>
       </c>
-      <c r="T7" s="16"/>
-      <c r="V7" s="15" t="s">
+      <c r="T7" s="25"/>
+      <c r="V7" s="26" t="s">
         <v>423</v>
       </c>
-      <c r="W7" s="15"/>
-      <c r="X7" s="17">
+      <c r="W7" s="26"/>
+      <c r="X7" s="24">
         <f>Analysis!B6</f>
         <v>723</v>
       </c>
-      <c r="Y7" s="16"/>
-      <c r="AA7" s="26" t="s">
+      <c r="Y7" s="25"/>
+      <c r="AA7" s="23" t="s">
         <v>484</v>
       </c>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="17">
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="24">
         <f>Analysis!B7</f>
         <v>22</v>
       </c>
-      <c r="AD7" s="16"/>
+      <c r="AD7" s="25"/>
     </row>
     <row r="8" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
     </row>
     <row r="9" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="D10" s="10"/>
@@ -28582,13 +28582,18 @@
       </c>
     </row>
     <row r="79" spans="8:9" ht="26" x14ac:dyDescent="0.6">
-      <c r="H79" s="19" t="s">
+      <c r="H79" s="22" t="s">
         <v>426</v>
       </c>
-      <c r="I79" s="18"/>
+      <c r="I79" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="D7:E9"/>
+    <mergeCell ref="L7:M9"/>
+    <mergeCell ref="G7:H9"/>
+    <mergeCell ref="I7:J9"/>
     <mergeCell ref="H79:I79"/>
     <mergeCell ref="AA7:AB9"/>
     <mergeCell ref="AC7:AD9"/>
@@ -28597,11 +28602,6 @@
     <mergeCell ref="Q7:R9"/>
     <mergeCell ref="S7:T9"/>
     <mergeCell ref="V7:W9"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="D7:E9"/>
-    <mergeCell ref="L7:M9"/>
-    <mergeCell ref="G7:H9"/>
-    <mergeCell ref="I7:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -28630,15 +28630,15 @@
       <c r="A1" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="J1" s="18" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="J1" s="21" t="s">
         <v>475</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -28658,7 +28658,7 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="16" t="s">
         <v>431</v>
       </c>
       <c r="C3" t="s">
@@ -28763,115 +28763,115 @@
         <v>466</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
+    <row r="13" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="15" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="15" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="21" t="s">
+    <row r="15" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="15" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="116" x14ac:dyDescent="0.35">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="15" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="116" x14ac:dyDescent="0.35">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="15" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+    <row r="18" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="15" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="21" t="s">
+    <row r="19" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="15" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="15" t="s">
         <v>474</v>
       </c>
     </row>

--- a/Excel_jumia_dataset.xlsx
+++ b/Excel_jumia_dataset.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javan\Desktop\Jumia\Jumia_Product_Performance_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F556B953-CAE8-443C-8BF4-876A73D46180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC248F5D-75CB-49A4-9931-017173275038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="3600" windowWidth="14400" windowHeight="7340" firstSheet="1" activeTab="4" xr2:uid="{720439CB-7872-429C-94DD-03C07880A471}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{720439CB-7872-429C-94DD-03C07880A471}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel_jumia_dataset" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="488">
   <si>
     <t>Product</t>
   </si>
@@ -1331,9 +1331,6 @@
   </si>
   <si>
     <t>Rating Mix</t>
-  </si>
-  <si>
-    <t>Average</t>
   </si>
   <si>
     <t>Excellent</t>
@@ -2173,6 +2170,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2180,12 +2183,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3980,7 +3977,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Average</c:v>
+                  <c:v>Excellent</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4019,13 +4016,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4045,7 +4042,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Excellent</c:v>
+                  <c:v>Missing</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4084,20 +4081,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A63A-4408-87AA-90301E16EDE4}"/>
+              <c16:uniqueId val="{00000001-2F88-4EE2-A949-5DF38EB02B20}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4110,7 +4107,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Missing</c:v>
+                  <c:v>Poor</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4149,85 +4146,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>35</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A63A-4408-87AA-90301E16EDE4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_Tables!$Q$18:$Q$19</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Poor</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot_Tables!$M$20:$M$23</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>High Discount</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Low Discount</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Medium Discount</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_Tables!$Q$20:$Q$23</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A63A-4408-87AA-90301E16EDE4}"/>
+              <c16:uniqueId val="{00000002-2F88-4EE2-A949-5DF38EB02B20}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9182,19 +9114,16 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_Tables!$A$15:$A$19</c:f>
+              <c:f>Pivot_Tables!$A$15:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Average</c:v>
+                  <c:v>Excellent</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Excellent</c:v>
+                  <c:v>Missing</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Missing</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>Poor</c:v>
                 </c:pt>
               </c:strCache>
@@ -9202,20 +9131,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_Tables!$B$15:$B$19</c:f>
+              <c:f>Pivot_Tables!$B$15:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>26</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
@@ -18128,230 +18054,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{896C9B17-5049-4235-98A2-4339E6CD5682}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="H18:I29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="110">
-        <item x="38"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="27"/>
-        <item x="31"/>
-        <item x="61"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="101"/>
-        <item x="80"/>
-        <item x="5"/>
-        <item x="100"/>
-        <item x="91"/>
-        <item x="47"/>
-        <item x="73"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="19"/>
-        <item x="74"/>
-        <item x="20"/>
-        <item x="94"/>
-        <item x="12"/>
-        <item x="40"/>
-        <item x="21"/>
-        <item x="58"/>
-        <item x="28"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="79"/>
-        <item x="60"/>
-        <item x="106"/>
-        <item x="90"/>
-        <item x="45"/>
-        <item x="76"/>
-        <item x="71"/>
-        <item x="97"/>
-        <item x="99"/>
-        <item x="67"/>
-        <item x="56"/>
-        <item x="15"/>
-        <item x="64"/>
-        <item x="96"/>
-        <item x="42"/>
-        <item x="78"/>
-        <item x="108"/>
-        <item x="49"/>
-        <item x="46"/>
-        <item x="83"/>
-        <item x="103"/>
-        <item x="44"/>
-        <item x="55"/>
-        <item x="36"/>
-        <item x="48"/>
-        <item x="75"/>
-        <item x="53"/>
-        <item x="7"/>
-        <item x="35"/>
-        <item x="72"/>
-        <item x="25"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="98"/>
-        <item x="68"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="39"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="102"/>
-        <item x="18"/>
-        <item x="77"/>
-        <item x="1"/>
-        <item x="95"/>
-        <item x="41"/>
-        <item x="14"/>
-        <item x="86"/>
-        <item x="29"/>
-        <item x="52"/>
-        <item x="59"/>
-        <item x="82"/>
-        <item x="84"/>
-        <item x="16"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="93"/>
-        <item x="26"/>
-        <item x="88"/>
-        <item x="37"/>
-        <item x="89"/>
-        <item x="43"/>
-        <item x="104"/>
-        <item x="54"/>
-        <item x="105"/>
-        <item x="63"/>
-        <item x="87"/>
-        <item x="92"/>
-        <item x="107"/>
-        <item x="85"/>
-        <item x="69"/>
-        <item x="3"/>
-        <item x="70"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="59"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="95"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="91"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Review" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B06BF4F-6313-49C4-BD21-FA374C57CBA6}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="M2:N13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -18564,6 +18266,262 @@
       </autoFilter>
     </filter>
   </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F36809F0-5F72-4343-8C12-581BE2C3BF82}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="M18:Q23" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0">
+      <items count="47">
+        <item x="44"/>
+        <item x="30"/>
+        <item x="33"/>
+        <item x="38"/>
+        <item x="42"/>
+        <item x="5"/>
+        <item x="41"/>
+        <item x="34"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="9"/>
+        <item x="43"/>
+        <item x="32"/>
+        <item x="19"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="36"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="39"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="35"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="11"/>
+        <item x="37"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="25"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="13"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="31"/>
+        <item x="45"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="24">
+        <item x="22"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Product" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -18889,7 +18847,7 @@
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49DCB90C-25D0-4471-842C-EAB3A6161C2D}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A14:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A14:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="2" showAll="0"/>
@@ -18926,7 +18884,7 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -18942,10 +18900,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="4">
     <i>
       <x v="1"/>
     </i>
@@ -19161,253 +19116,218 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F36809F0-5F72-4343-8C12-581BE2C3BF82}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="M18:R23" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{896C9B17-5049-4235-98A2-4339E6CD5682}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="H18:I29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="110">
+        <item x="38"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="27"/>
+        <item x="31"/>
+        <item x="61"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="101"/>
+        <item x="80"/>
+        <item x="5"/>
+        <item x="100"/>
+        <item x="91"/>
+        <item x="47"/>
+        <item x="73"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="19"/>
+        <item x="74"/>
+        <item x="20"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="58"/>
+        <item x="28"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="79"/>
+        <item x="60"/>
+        <item x="106"/>
+        <item x="90"/>
+        <item x="45"/>
+        <item x="76"/>
+        <item x="71"/>
+        <item x="97"/>
+        <item x="99"/>
+        <item x="67"/>
+        <item x="56"/>
+        <item x="15"/>
+        <item x="64"/>
+        <item x="96"/>
+        <item x="42"/>
+        <item x="78"/>
+        <item x="108"/>
+        <item x="49"/>
+        <item x="46"/>
+        <item x="83"/>
+        <item x="103"/>
+        <item x="44"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="75"/>
+        <item x="53"/>
+        <item x="7"/>
+        <item x="35"/>
+        <item x="72"/>
+        <item x="25"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="98"/>
+        <item x="68"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="39"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="102"/>
+        <item x="18"/>
+        <item x="77"/>
+        <item x="1"/>
+        <item x="95"/>
+        <item x="41"/>
+        <item x="14"/>
+        <item x="86"/>
+        <item x="29"/>
+        <item x="52"/>
+        <item x="59"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="16"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="93"/>
+        <item x="26"/>
+        <item x="88"/>
+        <item x="37"/>
+        <item x="89"/>
+        <item x="43"/>
+        <item x="104"/>
+        <item x="54"/>
+        <item x="105"/>
+        <item x="63"/>
+        <item x="87"/>
+        <item x="92"/>
+        <item x="107"/>
+        <item x="85"/>
+        <item x="69"/>
+        <item x="3"/>
+        <item x="70"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
     <pivotField numFmtId="2" showAll="0"/>
     <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0">
-      <items count="47">
-        <item x="44"/>
-        <item x="30"/>
-        <item x="33"/>
-        <item x="38"/>
-        <item x="42"/>
-        <item x="5"/>
-        <item x="41"/>
-        <item x="34"/>
-        <item x="40"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="9"/>
-        <item x="43"/>
-        <item x="32"/>
-        <item x="19"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="26"/>
-        <item x="36"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="39"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="35"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="11"/>
-        <item x="37"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="1"/>
-        <item x="25"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="13"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="31"/>
-        <item x="45"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="24">
-        <item x="22"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField numFmtId="2" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="7"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="11">
     <i>
-      <x/>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="18"/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="26"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Product" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Review" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="2" format="0" series="1">
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="2" format="1" series="1">
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -19446,7 +19366,7 @@
   <data>
     <tabular pivotCacheId="601624930">
       <items count="4">
-        <i x="0" s="1"/>
+        <i x="0"/>
         <i x="1" s="1"/>
         <i x="2" s="1"/>
         <i x="3" s="1"/>
@@ -26873,7 +26793,7 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="I1" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
@@ -26894,13 +26814,13 @@
         <v>3</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L2" s="19" t="s">
         <v>368</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N2" s="10"/>
     </row>
@@ -27007,7 +26927,7 @@
     </row>
     <row r="7" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B7" s="4">
         <f>COUNTIFS(tblProducts[Discount category],"High Discount",tblProducts[Rating category],"&lt;&gt;Excellent",tblProducts[Rating category],"&lt;&gt;Missing")</f>
@@ -27923,19 +27843,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD9B265-9AA4-496B-B0FD-1E21A0C8D1F9}">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="59.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="19" max="22" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="1.81640625" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="3.81640625" bestFit="1" customWidth="1"/>
@@ -27950,10 +27869,10 @@
         <v>408</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -27961,13 +27880,13 @@
         <v>402</v>
       </c>
       <c r="I2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>402</v>
       </c>
       <c r="N2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -28170,7 +28089,7 @@
         <v>410</v>
       </c>
       <c r="B15" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -28178,50 +28097,44 @@
         <v>411</v>
       </c>
       <c r="B16" s="11">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>412</v>
       </c>
       <c r="B17" s="11">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B18" s="11">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>402</v>
       </c>
       <c r="I18" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>407</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="B19" s="11">
-        <v>115</v>
-      </c>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="H19" s="13" t="s">
         <v>194</v>
       </c>
@@ -28241,13 +28154,10 @@
         <v>412</v>
       </c>
       <c r="Q19" t="s">
-        <v>413</v>
-      </c>
-      <c r="R19" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="H20" s="13" t="s">
         <v>30</v>
       </c>
@@ -28258,22 +28168,19 @@
         <v>403</v>
       </c>
       <c r="N20" s="11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O20" s="11">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="P20" s="11">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="11">
-        <v>10</v>
-      </c>
-      <c r="R20" s="11">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="H21" s="13" t="s">
         <v>89</v>
       </c>
@@ -28284,22 +28191,19 @@
         <v>404</v>
       </c>
       <c r="N21" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="11">
+        <v>14</v>
+      </c>
+      <c r="P21" s="11">
         <v>1</v>
       </c>
-      <c r="P21" s="11">
-        <v>14</v>
-      </c>
       <c r="Q21" s="11">
-        <v>1</v>
-      </c>
-      <c r="R21" s="11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="H22" s="13" t="s">
         <v>68</v>
       </c>
@@ -28310,24 +28214,21 @@
         <v>405</v>
       </c>
       <c r="N22" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O22" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P22" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="11">
-        <v>1</v>
-      </c>
-      <c r="R22" s="11">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>44</v>
@@ -28339,27 +28240,24 @@
         <v>406</v>
       </c>
       <c r="N23" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O23" s="11">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="P23" s="11">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="Q23" s="11">
-        <v>12</v>
-      </c>
-      <c r="R23" s="11">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>402</v>
       </c>
       <c r="B24" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>333</v>
@@ -28368,7 +28266,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
         <v>403</v>
       </c>
@@ -28382,7 +28280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
         <v>404</v>
       </c>
@@ -28396,7 +28294,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
         <v>405</v>
       </c>
@@ -28410,7 +28308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
         <v>406</v>
       </c>
@@ -28424,7 +28322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="H29" s="13" t="s">
         <v>406</v>
       </c>
@@ -28456,112 +28354,112 @@
       <c r="M5" s="14"/>
     </row>
     <row r="7" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="22" t="s">
         <v>375</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="25">
+      <c r="C7" s="22"/>
+      <c r="D7" s="23">
         <f>Analysis!B2</f>
         <v>115</v>
       </c>
-      <c r="E7" s="25"/>
-      <c r="G7" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="25">
+      <c r="E7" s="23"/>
+      <c r="G7" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="23">
         <f>Analysis!B3</f>
         <v>1172.7913043478261</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="L7" s="26" t="s">
-        <v>421</v>
-      </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="25">
+      <c r="J7" s="23"/>
+      <c r="L7" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="23">
         <f>Analysis!B4</f>
         <v>0.36956521739130432</v>
       </c>
-      <c r="O7" s="25"/>
-      <c r="Q7" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="R7" s="26"/>
-      <c r="S7" s="25">
+      <c r="O7" s="23"/>
+      <c r="Q7" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="R7" s="22"/>
+      <c r="S7" s="23">
         <f>Analysis!B5</f>
         <v>3.8894736842105258</v>
       </c>
-      <c r="T7" s="25"/>
-      <c r="V7" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="W7" s="26"/>
-      <c r="X7" s="24">
+      <c r="T7" s="23"/>
+      <c r="V7" s="22" t="s">
+        <v>422</v>
+      </c>
+      <c r="W7" s="22"/>
+      <c r="X7" s="26">
         <f>Analysis!B6</f>
         <v>723</v>
       </c>
-      <c r="Y7" s="25"/>
-      <c r="AA7" s="23" t="s">
-        <v>484</v>
-      </c>
-      <c r="AB7" s="23"/>
-      <c r="AC7" s="24">
+      <c r="Y7" s="23"/>
+      <c r="AA7" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="26">
         <f>Analysis!B7</f>
         <v>22</v>
       </c>
-      <c r="AD7" s="25"/>
+      <c r="AD7" s="23"/>
     </row>
     <row r="8" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="25"/>
-      <c r="Y8" s="25"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
     </row>
     <row r="9" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="D10" s="10"/>
@@ -28582,18 +28480,13 @@
       </c>
     </row>
     <row r="79" spans="8:9" ht="26" x14ac:dyDescent="0.6">
-      <c r="H79" s="22" t="s">
-        <v>426</v>
+      <c r="H79" s="24" t="s">
+        <v>425</v>
       </c>
       <c r="I79" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="D7:E9"/>
-    <mergeCell ref="L7:M9"/>
-    <mergeCell ref="G7:H9"/>
-    <mergeCell ref="I7:J9"/>
     <mergeCell ref="H79:I79"/>
     <mergeCell ref="AA7:AB9"/>
     <mergeCell ref="AC7:AD9"/>
@@ -28602,6 +28495,11 @@
     <mergeCell ref="Q7:R9"/>
     <mergeCell ref="S7:T9"/>
     <mergeCell ref="V7:W9"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="D7:E9"/>
+    <mergeCell ref="L7:M9"/>
+    <mergeCell ref="G7:H9"/>
+    <mergeCell ref="I7:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -28628,12 +28526,12 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
       <c r="J1" s="21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K1" s="21"/>
       <c r="L1" s="21"/>
@@ -28642,16 +28540,16 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2" t="s">
         <v>428</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>429</v>
       </c>
-      <c r="C2" t="s">
-        <v>430</v>
-      </c>
       <c r="J2" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -28659,13 +28557,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -28673,13 +28571,13 @@
         <v>374</v>
       </c>
       <c r="B4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -28687,13 +28585,13 @@
         <v>373</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -28701,13 +28599,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K6" s="10"/>
     </row>
@@ -28716,13 +28614,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -28730,149 +28628,149 @@
         <v>368</v>
       </c>
       <c r="B8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="K9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B11" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
